--- a/data/trans_dic/P16A09-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P16A09-Estudios-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido medicamentos para el reuma en las dos últimas semanas</t>
+          <t>Población que ha consumido medicamentos para el reuma en las dos últimas semanas (tasa de respuesta: 99,9%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>5,28; 8,28</t>
+          <t>5,35; 8,4</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2,73; 5,4</t>
+          <t>2,8; 5,53</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,4; 4,95</t>
+          <t>2,43; 5,01</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3,33; 6,38</t>
+          <t>3,19; 6,47</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>8,74; 11,94</t>
+          <t>8,51; 11,86</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>10,65; 14,3</t>
+          <t>10,91; 14,55</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>7,57; 11,38</t>
+          <t>7,61; 11,33</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>11,14; 15,57</t>
+          <t>11,2; 15,57</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>7,43; 9,77</t>
+          <t>7,47; 9,76</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>7,75; 10,11</t>
+          <t>7,79; 10,29</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>5,7; 8,0</t>
+          <t>5,78; 8,27</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>8,42; 11,17</t>
+          <t>8,23; 11,19</t>
         </is>
       </c>
     </row>
@@ -857,7 +857,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,78; 1,85</t>
+          <t>0,7; 1,88</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -867,52 +867,52 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,51; 1,42</t>
+          <t>0,48; 1,37</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,97; 2,15</t>
+          <t>1,0; 2,14</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,09; 2,41</t>
+          <t>1,15; 2,44</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,13; 2,51</t>
+          <t>1,27; 2,59</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,31; 2,64</t>
+          <t>1,32; 2,55</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>2,16; 3,82</t>
+          <t>2,22; 3,82</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,07; 1,96</t>
+          <t>1,06; 1,89</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1,14; 2,0</t>
+          <t>1,15; 1,99</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1,02; 1,75</t>
+          <t>1,02; 1,79</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>1,85; 2,81</t>
+          <t>1,77; 2,76</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,41; 2,64</t>
+          <t>0,39; 2,62</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,44; 3,42</t>
+          <t>0,44; 3,45</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,38</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,88</t>
+          <t>0,0; 0,9</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,23; 4,36</t>
+          <t>1,24; 4,31</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,56; 2,99</t>
+          <t>0,48; 3,0</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,2; 1,82</t>
+          <t>0,19; 1,93</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2,05; 4,21</t>
+          <t>2,0; 4,26</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,98; 2,77</t>
+          <t>1,05; 2,89</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,76; 2,52</t>
+          <t>0,68; 2,54</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,1; 0,88</t>
+          <t>0,09; 0,99</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1,09; 2,22</t>
+          <t>1,1; 2,21</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,35; 3,54</t>
+          <t>2,39; 3,5</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,61; 2,7</t>
+          <t>1,61; 2,68</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,97; 1,81</t>
+          <t>0,97; 1,75</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,34; 2,26</t>
+          <t>1,31; 2,24</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>4,38; 5,9</t>
+          <t>4,33; 5,87</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>5,06; 6,65</t>
+          <t>5,07; 6,67</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,2; 4,54</t>
+          <t>3,14; 4,51</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>4,14; 5,79</t>
+          <t>4,11; 5,81</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>3,54; 4,48</t>
+          <t>3,55; 4,53</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>3,52; 4,47</t>
+          <t>3,54; 4,54</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>2,21; 3,02</t>
+          <t>2,22; 3,0</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>2,99; 3,96</t>
+          <t>2,97; 3,89</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido medicamentos para el reuma en las dos últimas semanas</t>
+          <t>Población que ha consumido medicamentos para el reuma en las dos últimas semanas (tasa de respuesta: 99,9%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>54498; 85409</t>
+          <t>55165; 86627</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>26514; 52456</t>
+          <t>27215; 53747</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>18123; 37305</t>
+          <t>18315; 37818</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>17072; 32701</t>
+          <t>16365; 33152</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>114943; 157034</t>
+          <t>111953; 155940</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>141765; 190380</t>
+          <t>145301; 193749</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>75263; 113183</t>
+          <t>75699; 112674</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>83709; 117043</t>
+          <t>84175; 117046</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>174459; 229209</t>
+          <t>175413; 229031</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>178478; 232801</t>
+          <t>179361; 236947</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>99711; 139860</t>
+          <t>101091; 144656</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>106480; 141280</t>
+          <t>104068; 141456</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>13126; 31381</t>
+          <t>11793; 31779</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>16497; 38133</t>
+          <t>16458; 38233</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>10573; 29397</t>
+          <t>9898; 28524</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>22190; 49184</t>
+          <t>22946; 48985</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>17309; 38253</t>
+          <t>18233; 38803</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>19854; 43979</t>
+          <t>22223; 45378</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>26004; 52488</t>
+          <t>26255; 50786</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>48270; 85413</t>
+          <t>49753; 85476</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>35182; 64273</t>
+          <t>34778; 61964</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>42486; 74284</t>
+          <t>42861; 73817</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>41389; 70953</t>
+          <t>41462; 72558</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>83936; 127093</t>
+          <t>80231; 124995</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>2240; 14557</t>
+          <t>2165; 14474</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>2097; 16448</t>
+          <t>2114; 16588</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 2092</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 5703</t>
+          <t>0; 5834</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>5871; 20781</t>
+          <t>5901; 20514</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2542; 13695</t>
+          <t>2181; 13723</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>1079; 9976</t>
+          <t>1069; 10597</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>13536; 27754</t>
+          <t>13204; 28110</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>10083; 28481</t>
+          <t>10821; 29670</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>7088; 23658</t>
+          <t>6378; 23853</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>1073; 9657</t>
+          <t>997; 10869</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>14286; 29054</t>
+          <t>14396; 28915</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>77076; 115878</t>
+          <t>78300; 114764</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>54949; 92008</t>
+          <t>54954; 91355</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>32870; 61020</t>
+          <t>32613; 59103</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>46382; 78129</t>
+          <t>45038; 77184</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>147850; 199364</t>
+          <t>146473; 198455</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>179173; 235364</t>
+          <t>179614; 236150</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>112952; 160305</t>
+          <t>110851; 159148</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>150931; 211240</t>
+          <t>149932; 212067</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>235279; 298426</t>
+          <t>236178; 301417</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>244940; 310583</t>
+          <t>245850; 315385</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>152363; 208598</t>
+          <t>153058; 207433</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>212294; 281018</t>
+          <t>210806; 276307</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P16A09-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P16A09-Estudios-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>12,88%</t>
+          <t>12,46%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>9,54%</t>
+          <t>9,13%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>5,35; 8,4</t>
+          <t>5,25; 8,31</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2,8; 5,53</t>
+          <t>2,82; 5,43</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,43; 5,01</t>
+          <t>2,39; 5,0</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3,19; 6,47</t>
+          <t>3,05; 6,1</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>8,51; 11,86</t>
+          <t>8,6; 11,99</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>10,91; 14,55</t>
+          <t>10,79; 14,4</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>7,61; 11,33</t>
+          <t>7,44; 11,25</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>11,2; 15,57</t>
+          <t>10,83; 14,36</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>7,47; 9,76</t>
+          <t>7,51; 9,7</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>7,79; 10,29</t>
+          <t>7,79; 10,12</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>5,78; 8,27</t>
+          <t>5,76; 8,17</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>8,23; 11,19</t>
+          <t>7,93; 10,43</t>
         </is>
       </c>
     </row>
@@ -804,39 +804,39 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
+          <t>1,76%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>1,69%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>1,82%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>1,88%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>3,52%</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>1,44%</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
           <t>1,55%</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>1,69%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>1,82%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>1,88%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>3,05%</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>1,44%</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>1,55%</t>
-        </is>
-      </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
           <t>1,35%</t>
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,63%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,7; 1,88</t>
+          <t>0,73; 1,81</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,84; 1,95</t>
+          <t>0,86; 1,95</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,48; 1,37</t>
+          <t>0,49; 1,39</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,0; 2,14</t>
+          <t>1,24; 2,33</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,15; 2,44</t>
+          <t>1,14; 2,56</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,27; 2,59</t>
+          <t>1,24; 2,61</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,32; 2,55</t>
+          <t>1,3; 2,64</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>2,22; 3,82</t>
+          <t>2,93; 4,29</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,06; 1,89</t>
+          <t>1,07; 1,95</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1,15; 1,99</t>
+          <t>1,17; 2,0</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1,02; 1,79</t>
+          <t>0,99; 1,76</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>1,77; 2,76</t>
+          <t>2,25; 3,08</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,7%</t>
         </is>
       </c>
     </row>
@@ -997,12 +997,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,39; 2,62</t>
+          <t>0,44; 2,54</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,44; 3,45</t>
+          <t>0,44; 3,57</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -1012,47 +1012,47 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,9</t>
+          <t>0,0; 0,71</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,24; 4,31</t>
+          <t>1,19; 4,21</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,48; 3,0</t>
+          <t>0,65; 2,82</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,19; 1,93</t>
+          <t>0,2; 1,77</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2,0; 4,26</t>
+          <t>2,23; 4,49</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,05; 2,89</t>
+          <t>1,03; 2,77</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,68; 2,54</t>
+          <t>0,76; 2,66</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,09; 0,99</t>
+          <t>0,1; 0,98</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1,1; 2,21</t>
+          <t>1,2; 2,43</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>5,42%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,7%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,39; 3,5</t>
+          <t>2,4; 3,52</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,61; 2,68</t>
+          <t>1,61; 2,69</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,97; 1,75</t>
+          <t>0,96; 1,72</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,31; 2,24</t>
+          <t>1,46; 2,34</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>4,33; 5,87</t>
+          <t>4,35; 5,95</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>5,07; 6,67</t>
+          <t>5,03; 6,69</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,14; 4,51</t>
+          <t>3,22; 4,49</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>4,11; 5,81</t>
+          <t>4,79; 6,0</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>3,55; 4,53</t>
+          <t>3,54; 4,5</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>3,54; 4,54</t>
+          <t>3,52; 4,45</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>2,22; 3,0</t>
+          <t>2,21; 3,02</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>2,97; 3,89</t>
+          <t>3,38; 4,09</t>
         </is>
       </c>
     </row>
@@ -1451,7 +1451,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>23770</t>
+          <t>25337</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>96846</t>
+          <t>102122</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>120616</t>
+          <t>127458</t>
         </is>
       </c>
     </row>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>55165; 86627</t>
+          <t>54156; 85748</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>27215; 53747</t>
+          <t>27400; 52752</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>18315; 37818</t>
+          <t>18058; 37712</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>16365; 33152</t>
+          <t>17587; 35122</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>111953; 155940</t>
+          <t>113087; 157703</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>145301; 193749</t>
+          <t>143738; 191788</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>75699; 112674</t>
+          <t>74047; 111939</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>84175; 117046</t>
+          <t>88773; 117698</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>175413; 229031</t>
+          <t>176255; 227713</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>179361; 236947</t>
+          <t>179459; 233103</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>101091; 144656</t>
+          <t>100720; 142925</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>104068; 141456</t>
+          <t>110724; 145540</t>
         </is>
       </c>
     </row>
@@ -1659,7 +1659,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>35452</t>
+          <t>39157</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1679,7 +1679,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>68226</t>
+          <t>76401</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>103677</t>
+          <t>115558</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>11793; 31779</t>
+          <t>12325; 30587</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>16458; 38233</t>
+          <t>16759; 38165</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>9898; 28524</t>
+          <t>10239; 28831</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>22946; 48985</t>
+          <t>27600; 52011</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>18233; 38803</t>
+          <t>18091; 40639</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>22223; 45378</t>
+          <t>21726; 45744</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>26255; 50786</t>
+          <t>25928; 52393</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>49753; 85476</t>
+          <t>63660; 93019</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>34778; 61964</t>
+          <t>35082; 63942</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>42861; 73817</t>
+          <t>43453; 74183</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>41462; 72558</t>
+          <t>40333; 71658</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>80231; 124995</t>
+          <t>98988; 135632</t>
         </is>
       </c>
     </row>
@@ -1867,7 +1867,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1387</t>
+          <t>1307</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1887,7 +1887,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>19415</t>
+          <t>23310</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1907,7 +1907,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>20803</t>
+          <t>24617</t>
         </is>
       </c>
     </row>
@@ -1920,12 +1920,12 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>2165; 14474</t>
+          <t>2424; 14018</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>2114; 16588</t>
+          <t>2108; 17130</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -1935,47 +1935,47 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 5834</t>
+          <t>0; 5059</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>5901; 20514</t>
+          <t>5673; 20054</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2181; 13723</t>
+          <t>2979; 12924</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>1069; 10597</t>
+          <t>1078; 9720</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>13204; 28110</t>
+          <t>16336; 32958</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>10821; 29670</t>
+          <t>10558; 28444</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>6378; 23853</t>
+          <t>7161; 24952</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>997; 10869</t>
+          <t>1089; 10769</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>14396; 28915</t>
+          <t>17356; 35130</t>
         </is>
       </c>
     </row>
@@ -2075,7 +2075,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>60609</t>
+          <t>65800</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2095,7 +2095,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>184487</t>
+          <t>201833</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>245096</t>
+          <t>267633</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>78300; 114764</t>
+          <t>78523; 115374</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>54954; 91355</t>
+          <t>55034; 91699</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>32613; 59103</t>
+          <t>32570; 57984</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>45038; 77184</t>
+          <t>51285; 82494</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>146473; 198455</t>
+          <t>147081; 200905</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>179614; 236150</t>
+          <t>178043; 236958</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>110851; 159148</t>
+          <t>113559; 158544</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>149932; 212067</t>
+          <t>178374; 223618</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>236178; 301417</t>
+          <t>235431; 299774</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>245850; 315385</t>
+          <t>244820; 309492</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>153058; 207433</t>
+          <t>152490; 208991</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>210806; 276307</t>
+          <t>244570; 295883</t>
         </is>
       </c>
     </row>
